--- a/employee_surveys/048_employee_benefits_knowledge_quiz--employee_surveys.xlsx
+++ b/employee_surveys/048_employee_benefits_knowledge_quiz--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'health_insurance'}</t>
+          <t>health_insurance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Health Insurance'}</t>
+          <t>Health Insurance</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'retirement_plan'}</t>
+          <t>retirement_plan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Retirement Plan'}</t>
+          <t>Retirement Plan</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'life_insurance'}</t>
+          <t>life_insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Life Insurance'}</t>
+          <t>Life Insurance</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'disability_insurance'}</t>
+          <t>disability_insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Disability Insurance'}</t>
+          <t>Disability Insurance</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'health_savings_plan'}</t>
+          <t>health_savings_plan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Health Savings Plan'}</t>
+          <t>Health Savings Plan</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'flexible_spending_account'}</t>
+          <t>flexible_spending_account</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Flexible Spending Account'}</t>
+          <t>Flexible Spending Account</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dependent_care_assistance'}</t>
+          <t>dependent_care_assistance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dependent Care Assistance'}</t>
+          <t>Dependent Care Assistance</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'home_and_auto'}</t>
+          <t>home_and_auto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Home and Auto'}</t>
+          <t>Home and Auto</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'long-term_care_insurance'}</t>
+          <t>long-term_care_insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Long-Term Care Insurance'}</t>
+          <t>Long-Term Care Insurance</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'short-term_care_insurance'}</t>
+          <t>short-term_care_insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Short-Term Care Insurance'}</t>
+          <t>Short-Term Care Insurance</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'disability_insurance'}</t>
+          <t>disability_insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Disability Insurance'}</t>
+          <t>Disability Insurance</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'life_insurance'}</t>
+          <t>life_insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Life Insurance'}</t>
+          <t>Life Insurance</t>
         </is>
       </c>
     </row>
